--- a/pkpdapp/pkpdapp/migrations/models/ParametersValue_Species.xlsx
+++ b/pkpdapp/pkpdapp/migrations/models/ParametersValue_Species.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gertzm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrobins/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{595F668E-A8EA-4FDB-85B1-F4027503F1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD79781-C6AF-F84D-BF76-769FDE5D67D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="1200" windowWidth="29020" windowHeight="18880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cmpt_PK_Model" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="47">
   <si>
     <t>SM_Mouse</t>
   </si>
@@ -174,6 +174,15 @@
   <si>
     <t>CLdif</t>
   </si>
+  <si>
+    <t>ng/mL</t>
+  </si>
+  <si>
+    <t>Vmax</t>
+  </si>
+  <si>
+    <t>µg/h/kg</t>
+  </si>
 </sst>
 </file>
 
@@ -245,21 +254,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -548,584 +552,584 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>0.05</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4">
         <v>0.04</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.01</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.5</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.5</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>80</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>80</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>4</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>80</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>300</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>6000</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>540</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.35</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>330</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0.4</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>260</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="7">
         <v>0.25</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>10</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>8</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>B7</f>
         <v>540</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>D7</f>
         <v>0.35</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>F7</f>
         <v>330</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <f>H7</f>
         <v>0.4</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <f>J7</f>
         <v>260</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <f>L7</f>
         <v>0.25</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <f>N7</f>
         <v>10</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="5">
         <f>P7</f>
         <v>8</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>5000</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="7">
         <v>5</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="5">
         <v>5000</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="7">
         <v>5</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="I9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="5">
         <v>5000</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="9">
+      <c r="K9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="7">
         <v>5</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" s="6">
+      <c r="M9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="5">
         <v>5000</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" s="9">
+      <c r="O9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="7">
         <v>5</v>
       </c>
-      <c r="Q9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="Q9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>0.1</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5">
         <v>0.1</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5">
         <v>0.1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5">
         <v>0.1</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="I10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5">
         <v>0.1</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="5">
         <v>0.1</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="M10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="5">
         <v>0.1</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="6">
+      <c r="O10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="Q10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>0.01</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5">
         <v>0.2</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5">
         <v>0.01</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="4">
         <v>0.2</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="I11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="5">
         <v>0.01</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="5">
         <v>0.2</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="M11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="5">
         <v>0.01</v>
       </c>
-      <c r="O11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" s="6">
+      <c r="O11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1138,728 +1142,728 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>0.05</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
         <v>0.04</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.01</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.5</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.5</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="8">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>40</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>150</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>3000</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>B6</f>
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="3" t="str">
         <f t="shared" ref="C7:Q7" si="0">C6</f>
         <v>L/kg</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>40</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K7" s="4" t="str">
+      <c r="K7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="M7" s="4" t="str">
+      <c r="M7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="O7" s="4" t="str">
+      <c r="O7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>3000</v>
       </c>
-      <c r="Q7" s="4" t="str">
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>'1cmpt_PK_Model'!B7</f>
         <v>540</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>'1cmpt_PK_Model'!D7</f>
         <v>0.35</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>'1cmpt_PK_Model'!F7</f>
         <v>330</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <f>'1cmpt_PK_Model'!H7</f>
         <v>0.4</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <f>'1cmpt_PK_Model'!J7</f>
         <v>260</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <f>'1cmpt_PK_Model'!L7</f>
         <v>0.25</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <f>'1cmpt_PK_Model'!N7</f>
         <v>10</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="7">
         <f>'1cmpt_PK_Model'!P7</f>
         <v>8</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <f>B8*5</f>
         <v>2700</v>
       </c>
-      <c r="C9" s="4" t="str">
+      <c r="C9" s="3" t="str">
         <f t="shared" ref="C9:Q9" si="1">C8</f>
         <v>mL/h/kg</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <f>D8*5</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="4" t="str">
+      <c r="E9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f>F8*5</f>
         <v>1650</v>
       </c>
-      <c r="G9" s="4" t="str">
+      <c r="G9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="7">
         <f>H8*5</f>
         <v>2</v>
       </c>
-      <c r="I9" s="4" t="str">
+      <c r="I9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <f>J8*5</f>
         <v>1300</v>
       </c>
-      <c r="K9" s="4" t="str">
+      <c r="K9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <f>L8*5</f>
         <v>1.25</v>
       </c>
-      <c r="M9" s="4" t="str">
+      <c r="M9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <f>N8*5</f>
         <v>50</v>
       </c>
-      <c r="O9" s="4" t="str">
+      <c r="O9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>L/h</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <f>P8*5</f>
         <v>40</v>
       </c>
-      <c r="Q9" s="4" t="str">
+      <c r="Q9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <f>B8</f>
         <v>540</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f>D8</f>
         <v>0.35</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <f>F8</f>
         <v>330</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <f>H8</f>
         <v>0.4</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <f>J8</f>
         <v>260</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <f>L8</f>
         <v>0.25</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <f>N8</f>
         <v>10</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <f>P8</f>
         <v>8</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>5000</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="5">
         <v>5000</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="7">
         <v>5</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="I11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="5">
         <v>5000</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="K11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="7">
         <v>5</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="M11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="5">
         <v>5000</v>
       </c>
-      <c r="O11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="9">
+      <c r="O11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="7">
         <v>5</v>
       </c>
-      <c r="Q11" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>0.1</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="6">
         <v>0.1</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="6">
         <v>0.1</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="G12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="6">
         <v>0.1</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="8">
+      <c r="I12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6">
         <v>0.1</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="K12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="6">
         <v>0.1</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="8">
+      <c r="M12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="6">
         <v>0.1</v>
       </c>
-      <c r="O12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="O12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="6">
         <v>0.1</v>
       </c>
-      <c r="Q12" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>0.01</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="5">
         <v>0.2</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="5">
         <v>0.01</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="7">
+      <c r="G13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="5">
         <v>0.2</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="I13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="5">
         <v>0.01</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="5">
         <v>0.2</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="6">
+      <c r="M13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="5">
         <v>0.01</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="6">
+      <c r="O13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1872,864 +1876,864 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>0.05</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
         <v>0.04</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.01</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.5</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.5</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="8">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>40</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>150</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>3000</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="3" t="str">
         <f t="shared" ref="C7:Q8" si="0">C6</f>
         <v>L/kg</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>40</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K7" s="4" t="str">
+      <c r="K7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="M7" s="4" t="str">
+      <c r="M7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="O7" s="4" t="str">
+      <c r="O7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>3000</v>
       </c>
-      <c r="Q7" s="4" t="str">
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>mL</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>B7/2</f>
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="str">
+      <c r="C8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>D7/2</f>
         <v>20</v>
       </c>
-      <c r="E8" s="4" t="str">
+      <c r="E8" s="3" t="str">
         <f>E7</f>
         <v>mL/kg</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>F7/2</f>
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="str">
+      <c r="G8" s="3" t="str">
         <f>G7</f>
         <v>L/kg</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <f>H7/2</f>
         <v>20</v>
       </c>
-      <c r="I8" s="4" t="str">
+      <c r="I8" s="3" t="str">
         <f>I7</f>
         <v>mL/kg</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="7">
         <f>J7/2</f>
         <v>1</v>
       </c>
-      <c r="K8" s="4" t="str">
+      <c r="K8" s="3" t="str">
         <f>K7</f>
         <v>L/kg</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="8">
         <f>L7/2</f>
         <v>20</v>
       </c>
-      <c r="M8" s="4" t="str">
+      <c r="M8" s="3" t="str">
         <f>M7</f>
         <v>mL/kg</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <f>N7/2</f>
         <v>75</v>
       </c>
-      <c r="O8" s="4" t="str">
+      <c r="O8" s="3" t="str">
         <f>O7</f>
         <v>L</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="5">
         <f>P7/2</f>
         <v>1500</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <f>'1cmpt_PK_Model'!B7</f>
         <v>540</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f>'1cmpt_PK_Model'!D7</f>
         <v>0.35</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f>'1cmpt_PK_Model'!F7</f>
         <v>330</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <f>'1cmpt_PK_Model'!H7</f>
         <v>0.4</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <f>'1cmpt_PK_Model'!J7</f>
         <v>260</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <f>'1cmpt_PK_Model'!L7</f>
         <v>0.25</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <f>'1cmpt_PK_Model'!N7</f>
         <v>10</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="7">
         <f>'1cmpt_PK_Model'!P7</f>
         <v>8</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="Q9" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <f>B9*5</f>
         <v>2700</v>
       </c>
-      <c r="C10" s="4" t="str">
+      <c r="C10" s="3" t="str">
         <f t="shared" ref="C10:Q11" si="1">C9</f>
         <v>mL/h/kg</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <f>D9*5</f>
         <v>1.75</v>
       </c>
-      <c r="E10" s="4" t="str">
+      <c r="E10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <f>F9*5</f>
         <v>1650</v>
       </c>
-      <c r="G10" s="4" t="str">
+      <c r="G10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="7">
         <f>H9*5</f>
         <v>2</v>
       </c>
-      <c r="I10" s="4" t="str">
+      <c r="I10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <f>J9*5</f>
         <v>1300</v>
       </c>
-      <c r="K10" s="4" t="str">
+      <c r="K10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <f>L9*5</f>
         <v>1.25</v>
       </c>
-      <c r="M10" s="4" t="str">
+      <c r="M10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <f>N9*5</f>
         <v>50</v>
       </c>
-      <c r="O10" s="4" t="str">
+      <c r="O10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>L/h</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <f>P9*5</f>
         <v>40</v>
       </c>
-      <c r="Q10" s="4" t="str">
+      <c r="Q10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <f>B10/50</f>
         <v>54</v>
       </c>
-      <c r="C11" s="4" t="str">
+      <c r="C11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <f>D10/50</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E11" s="4" t="str">
+      <c r="E11" s="3" t="str">
         <f>E10</f>
         <v>mL/h/kg</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <f>F10/50</f>
         <v>33</v>
       </c>
-      <c r="G11" s="4" t="str">
+      <c r="G11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <f>H10/50</f>
         <v>0.04</v>
       </c>
-      <c r="I11" s="4" t="str">
+      <c r="I11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <f>J10/50</f>
         <v>26</v>
       </c>
-      <c r="K11" s="4" t="str">
+      <c r="K11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <f>L10/50</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M11" s="4" t="str">
+      <c r="M11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <f>N10/50</f>
         <v>1</v>
       </c>
-      <c r="O11" s="4" t="str">
+      <c r="O11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>L/h</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <f>P10/50</f>
         <v>0.8</v>
       </c>
-      <c r="Q11" s="4" t="str">
+      <c r="Q11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>mL/h</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <f>B9</f>
         <v>540</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <f>D9</f>
         <v>0.35</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <f>F9</f>
         <v>330</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <f>H9</f>
         <v>0.4</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <f>J9</f>
         <v>260</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f>L9</f>
         <v>0.25</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <f>N9</f>
         <v>10</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <f>P9</f>
         <v>8</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>5000</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="7">
         <v>5</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="5">
         <v>5000</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="7">
         <v>5</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="I13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="5">
         <v>5000</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="K13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="7">
         <v>5</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="6">
+      <c r="M13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="5">
         <v>5000</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P13" s="9">
+      <c r="O13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" s="7">
         <v>5</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>0.1</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6">
         <v>0.1</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="6">
         <v>0.1</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="13">
+      <c r="G14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6">
         <v>0.1</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="8">
+      <c r="I14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="6">
         <v>0.1</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="8">
+      <c r="K14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="6">
         <v>0.1</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="8">
+      <c r="M14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="6">
         <v>0.1</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="8">
+      <c r="O14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="6">
         <v>0.1</v>
       </c>
-      <c r="Q14" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>0.01</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="5">
         <v>0.2</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="5">
         <v>0.01</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="G15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="5">
         <v>0.2</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="6">
+      <c r="I15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="5">
         <v>0.01</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="K15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="5">
         <v>0.2</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="6">
+      <c r="M15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="5">
         <v>0.01</v>
       </c>
-      <c r="O15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="6">
+      <c r="O15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2741,768 +2745,873 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>0.05</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4">
         <v>0.04</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.01</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.5</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.5</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>80</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>80</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>4</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>80</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>300</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>6000</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>540</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.35</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>330</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0.4</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>260</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="7">
         <v>0.25</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>10</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>8</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>0.1</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5">
         <v>0.1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="5">
         <v>0.1</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5">
         <v>0.1</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="6">
+      <c r="I8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5">
         <v>0.1</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="5">
         <v>0.1</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="6">
+      <c r="M8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="5">
         <v>0.1</v>
       </c>
-      <c r="O8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="6">
+      <c r="O8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>0.01</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="5">
         <v>0.2</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="5">
         <v>0.01</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="4">
         <v>0.2</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="I9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="5">
         <v>0.01</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="K9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="5">
         <v>0.2</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="6">
+      <c r="M9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="5">
         <v>0.01</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" s="6">
+      <c r="O9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="Q9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="5">
         <f>F10</f>
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="5">
         <f>H10</f>
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="5">
         <f>J10</f>
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="I10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5">
         <f>L10</f>
         <v>1</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="5">
         <f>N10</f>
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="M10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="5">
         <f>P10</f>
         <v>1</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" s="6">
+      <c r="O10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" s="5">
         <v>1</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="Q10" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>5000</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="5">
         <v>5000</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="7">
         <v>5</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="I11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="5">
         <v>5000</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="K11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="7">
         <v>5</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="M11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="5">
         <v>5000</v>
       </c>
-      <c r="O11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="9">
+      <c r="O11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="7">
         <v>5</v>
       </c>
-      <c r="Q11" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="6">
         <f t="shared" ref="F12:N12" si="0">H12</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="6">
         <f t="shared" si="0"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="I12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5">
         <f t="shared" si="0"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="5">
         <f t="shared" si="0"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="6">
+      <c r="M12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="O12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="O12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="Q12" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="9">
         <f>(0.025/75)^-0.25*N13</f>
         <v>7.1248098515933986E-2</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="14">
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="9">
         <f>(0.025/75)^-0.25*P13</f>
         <v>7.1248098515933986E-2</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="E13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="9">
         <f>(0.25/75)^-0.25*N13</f>
         <v>4.0065750136742871E-2</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="G13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="9">
         <f>(0.25/75)^-0.25*P13</f>
         <v>4.0065750136742871E-2</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="I13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5">
         <f>(3.5/75)^-0.25*N13</f>
         <v>2.0712917213851895E-2</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="5">
         <f>(3.5/75)^-0.25*P13</f>
         <v>2.0712917213851895E-2</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="M13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="10">
         <f>P13</f>
         <v>9.6270441744436847E-3</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P13" s="15">
+      <c r="O13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="10">
         <f>LN(2)/72</f>
         <v>9.6270441744436847E-3</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <f>(0.025/75)^-0.25*N14</f>
         <v>0.35624049257966989</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6">
         <f>(0.025/75)^-0.25*P14</f>
         <v>0.35624049257966989</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="6">
         <f>(0.25/75)^-0.25*N14</f>
         <v>0.20032875068371434</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6">
         <f>(0.25/75)^-0.25*P14</f>
         <v>0.20032875068371434</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="6">
+      <c r="I14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5">
         <f>(3.5/75)^-0.25*N14</f>
         <v>0.10356458606925947</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="K14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="5">
         <f>(3.5/75)^-0.25*P14</f>
         <v>0.10356458606925947</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="M14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="10">
         <f>P14</f>
         <v>4.8135220872218422E-2</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="15">
+      <c r="O14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="10">
         <f>P13*5</f>
         <v>4.8135220872218422E-2</v>
       </c>
-      <c r="Q14" s="4" t="s">
-        <v>15</v>
+      <c r="Q14" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="5">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="5">
+        <v>5</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="5">
+        <v>5</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="5">
+        <v>50</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3512,919 +3621,1024 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>0.05</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
         <v>0.04</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="O4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.01</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.5</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.5</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.5</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="8">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>40</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>150</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>3000</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>B6</f>
         <v>2</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" t="str">
         <f t="shared" ref="C7:Q7" si="0">C6</f>
         <v>L/kg</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>40</v>
       </c>
-      <c r="E7" s="1" t="str">
+      <c r="E7" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="I7" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K7" s="1" t="str">
+      <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>L/kg</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="M7" s="1" t="str">
+      <c r="M7" t="str">
         <f t="shared" si="0"/>
         <v>mL/kg</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="O7" s="1" t="str">
+      <c r="O7" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <v>3000</v>
       </c>
-      <c r="Q7" s="1" t="str">
+      <c r="Q7" t="str">
         <f t="shared" si="0"/>
         <v>mL</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>'1cmpt_PK_Model'!B7</f>
         <v>540</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>'1cmpt_PK_Model'!D7</f>
         <v>0.35</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>'1cmpt_PK_Model'!F7</f>
         <v>330</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <f>'1cmpt_PK_Model'!H7</f>
         <v>0.4</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <f>'1cmpt_PK_Model'!J7</f>
         <v>260</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="6">
         <f>'1cmpt_PK_Model'!L7</f>
         <v>0.25</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <f>'1cmpt_PK_Model'!N7</f>
         <v>10</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="7">
         <f>'1cmpt_PK_Model'!P7</f>
         <v>8</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <f>B8*5</f>
         <v>2700</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" t="str">
         <f t="shared" ref="C9:Q9" si="1">C8</f>
         <v>mL/h/kg</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <f>D8*5</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="1" t="str">
+      <c r="E9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f>F8*5</f>
         <v>1650</v>
       </c>
-      <c r="G9" s="1" t="str">
+      <c r="G9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="7">
         <f>H8*5</f>
         <v>2</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="I9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <f>J8*5</f>
         <v>1300</v>
       </c>
-      <c r="K9" s="1" t="str">
+      <c r="K9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <f>L8*5</f>
         <v>1.25</v>
       </c>
-      <c r="M9" s="1" t="str">
+      <c r="M9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h/kg</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <f>N8*5</f>
         <v>50</v>
       </c>
-      <c r="O9" s="1" t="str">
+      <c r="O9" t="str">
         <f t="shared" si="1"/>
         <v>L/h</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <f>P8*5</f>
         <v>40</v>
       </c>
-      <c r="Q9" s="1" t="str">
+      <c r="Q9" t="str">
         <f t="shared" si="1"/>
         <v>mL/h</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>0.1</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5">
         <v>0.1</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5">
         <v>0.1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5">
         <v>0.1</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="I10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5">
         <v>0.1</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="5">
         <v>0.1</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="M10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="5">
         <v>0.1</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="6">
+      <c r="O10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="Q10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>0.01</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5">
         <v>0.2</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5">
         <v>0.01</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="4">
         <v>0.2</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="I11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="5">
         <v>0.01</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="5">
         <v>0.2</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="M11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="5">
         <v>0.01</v>
       </c>
-      <c r="O11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" s="6">
+      <c r="O11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="5">
         <f>F12</f>
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="5">
         <f>H12</f>
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="5">
         <f>J12</f>
         <v>1</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="I12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5">
         <f>L12</f>
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="5">
         <f>N12</f>
         <v>1</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="6">
+      <c r="M12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="5">
         <f>P12</f>
         <v>1</v>
       </c>
-      <c r="O12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" s="6">
+      <c r="O12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="5">
         <v>1</v>
       </c>
-      <c r="Q12" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>0.5</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5">
         <f t="shared" ref="D13:N14" si="2">F13</f>
         <v>0.5</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="5">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="5">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="I13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="5">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="5">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="6">
+      <c r="M13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="5">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P13" s="6">
+      <c r="O13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="6">
         <f t="shared" si="2"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6">
         <f t="shared" si="2"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="6">
+      <c r="I14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5">
         <f t="shared" si="2"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="K14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="5">
         <f t="shared" si="2"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="M14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="5">
         <f t="shared" si="2"/>
         <v>0.69314718055994529</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="8">
+      <c r="O14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="6">
         <f>LN(2)/1</f>
         <v>0.69314718055994529</v>
       </c>
-      <c r="Q14" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="9">
         <f>(0.025/75)^-0.25*N15</f>
         <v>7.1248098515933986E-2</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="9">
         <f>(0.025/75)^-0.25*P15</f>
         <v>7.1248098515933986E-2</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="E15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9">
         <f>(0.25/75)^-0.25*N15</f>
         <v>4.0065750136742871E-2</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="9">
         <f>(0.25/75)^-0.25*P15</f>
         <v>4.0065750136742871E-2</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="6">
+      <c r="I15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="5">
         <f>(3.5/75)^-0.25*N15</f>
         <v>2.0712917213851895E-2</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="K15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="5">
         <f>(3.5/75)^-0.25*P15</f>
         <v>2.0712917213851895E-2</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N15" s="15">
+      <c r="M15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="10">
         <f>P15</f>
         <v>9.6270441744436847E-3</v>
       </c>
-      <c r="O15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="15">
+      <c r="O15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="10">
         <f>LN(2)/72</f>
         <v>9.6270441744436847E-3</v>
       </c>
-      <c r="Q15" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="Q15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <f>(0.025/75)^-0.25*N16</f>
         <v>0.35624049257966989</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6">
         <f>(0.025/75)^-0.25*P16</f>
         <v>0.35624049257966989</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="6">
         <f>(0.25/75)^-0.25*N16</f>
         <v>0.20032875068371434</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="6">
         <f>(0.25/75)^-0.25*P16</f>
         <v>0.20032875068371434</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="6">
+      <c r="I16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="5">
         <f>(3.5/75)^-0.25*N16</f>
         <v>0.10356458606925947</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="K16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="5">
         <f>(3.5/75)^-0.25*P16</f>
         <v>0.10356458606925947</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="15">
+      <c r="M16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="10">
         <f>P16</f>
         <v>4.8135220872218422E-2</v>
       </c>
-      <c r="O16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P16" s="15">
+      <c r="O16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P16" s="10">
         <f>P15*5</f>
         <v>4.8135220872218422E-2</v>
       </c>
-      <c r="Q16" s="4" t="s">
-        <v>15</v>
+      <c r="Q16" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="5">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="5">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="5">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="5">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="5">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="5">
+        <v>50</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P18" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4435,345 +4649,344 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7825586-2041-4CEB-8FC0-08EFA1E81209}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="9">
         <v>0.02</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="6">
         <v>0.1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="10">
         <v>1.25E-3</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="6">
         <v>0.25</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="9">
         <v>0.01</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="6">
         <v>0.3</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="9">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="10">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="10">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="9">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="9">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="6">
         <v>0.09</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="6">
         <v>0.09</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="6">
         <v>0.15</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="6">
         <v>0.15</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="10">
         <f>5/1000</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="10">
         <f>5/1000</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="6">
         <v>0.125</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <v>0.125</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="6">
         <v>0.25</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="6">
         <v>0.25</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="10">
         <f>8/1000</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="10">
         <f>8/1000</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="9">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="9">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>1.8</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="7">
         <v>1.8</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="7">
         <v>4.2</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="7">
         <v>4.2</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="Q9" s="4"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="4"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
-      <c r="C11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="4"/>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B10" s="12"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B11" s="11"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pkpdapp/pkpdapp/migrations/models/ParametersValue_Species.xlsx
+++ b/pkpdapp/pkpdapp/migrations/models/ParametersValue_Species.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrobins/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD79781-C6AF-F84D-BF76-769FDE5D67D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5289CC86-B9E5-964C-86A6-4992113DF6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="1200" windowWidth="29020" windowHeight="18880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="1200" windowWidth="29020" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cmpt_PK_Model" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="51">
   <si>
     <t>SM_Mouse</t>
   </si>
@@ -182,6 +182,18 @@
   </si>
   <si>
     <t>µg/h/kg</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>µg/mL</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
   </si>
 </sst>
 </file>
@@ -551,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1133,6 +1145,43 @@
         <v>29</v>
       </c>
     </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1141,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1867,6 +1916,80 @@
         <v>29</v>
       </c>
     </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1875,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -2735,6 +2858,117 @@
       </c>
       <c r="Q15" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="K17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
